--- a/outputs/52532.xlsx
+++ b/outputs/52532.xlsx
@@ -137,12 +137,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,218 +342,218 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>433</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>345</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>223</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>306</v>
       </c>
-      <c r="H2" s="1" t="n">
-        <f aca="false">(B2=MAX(B$2:B$8))+(C2=MAX(C$2:C$8))+(D2=MAX(D$2:D$8))+(E2=MAX(E$2:E$8))+(F2=MAX(F$2:F$8))+(G2=MAX(G$2:G$8))</f>
+      <c r="H2" s="2" t="n">
+        <f aca="true">SUMPRODUCT(--(B2:G2=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B2:G2)-COLUMN(B$2),7,1))))/7</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>512</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>483</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>209</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>377</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>455</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <f aca="false">(B3=MAX(B$2:B$8))+(C3=MAX(C$2:C$8))+(D3=MAX(D$2:D$8))+(E3=MAX(E$2:E$8))+(F3=MAX(F$2:F$8))+(G3=MAX(G$2:G$8))</f>
+      <c r="H3" s="2" t="n">
+        <f aca="true">SUMPRODUCT(--(B3:G3=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B3:G3)-COLUMN(B$2),7,1))))/7</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>202</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>306</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>402</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>502</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>409</v>
       </c>
-      <c r="H4" s="1" t="n">
-        <f aca="false">(B4=MAX(B$2:B$8))+(C4=MAX(C$2:C$8))+(D4=MAX(D$2:D$8))+(E4=MAX(E$2:E$8))+(F4=MAX(F$2:F$8))+(G4=MAX(G$2:G$8))</f>
+      <c r="H4" s="2" t="n">
+        <f aca="true">SUMPRODUCT(--(B4:G4=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B4:G4)-COLUMN(B$2),7,1))))/7</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>388</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>398</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>209</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>318</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>227</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <f aca="false">(B5=MAX(B$2:B$8))+(C5=MAX(C$2:C$8))+(D5=MAX(D$2:D$8))+(E5=MAX(E$2:E$8))+(F5=MAX(F$2:F$8))+(G5=MAX(G$2:G$8))</f>
+      <c r="H5" s="2" t="n">
+        <f aca="true">SUMPRODUCT(--(B5:G5=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B5:G5)-COLUMN(B$2),7,1))))/7</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>411</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>271</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>329</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <v>198</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="H6" s="1" t="n">
-        <f aca="false">(B6=MAX(B$2:B$8))+(C6=MAX(C$2:C$8))+(D6=MAX(D$2:D$8))+(E6=MAX(E$2:E$8))+(F6=MAX(F$2:F$8))+(G6=MAX(G$2:G$8))</f>
+      <c r="H6" s="2" t="n">
+        <f aca="true">SUMPRODUCT(--(B6:G6=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B6:G6)-COLUMN(B$2),7,1))))/7</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>179</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>209</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>401</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <v>333</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>343</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <f aca="false">(B7=MAX(B$2:B$8))+(C7=MAX(C$2:C$8))+(D7=MAX(D$2:D$8))+(E7=MAX(E$2:E$8))+(F7=MAX(F$2:F$8))+(G7=MAX(G$2:G$8))</f>
+      <c r="H7" s="2" t="n">
+        <f aca="true">SUMPRODUCT(--(B7:G7=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B7:G7)-COLUMN(B$2),7,1))))/7</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>309</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>238</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>298</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>254</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>199</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <f aca="false">(B8=MAX(B$2:B$8))+(C8=MAX(C$2:C$8))+(D8=MAX(D$2:D$8))+(E8=MAX(E$2:E$8))+(F8=MAX(F$2:F$8))+(G8=MAX(G$2:G$8))</f>
+      <c r="H8" s="2" t="n">
+        <f aca="true">SUMPRODUCT(--(B8:G8=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B8:G8)-COLUMN(B$2),7,1))))/7</f>
         <v>0</v>
       </c>
     </row>

--- a/outputs/52532.xlsx
+++ b/outputs/52532.xlsx
@@ -391,8 +391,8 @@
         <v>306</v>
       </c>
       <c r="H2" s="2" t="n">
-        <f aca="true">SUMPRODUCT(--(B2:G2=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B2:G2)-COLUMN(B$2),7,1))))/7</f>
-        <v>0</v>
+        <f aca="false">SUMPRODUCT(($B2:$G2=MAX($B2:$G2)))*1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -418,8 +418,8 @@
         <v>118</v>
       </c>
       <c r="H3" s="2" t="n">
-        <f aca="true">SUMPRODUCT(--(B3:G3=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B3:G3)-COLUMN(B$2),7,1))))/7</f>
-        <v>2</v>
+        <f aca="false">SUMPRODUCT(($B2:$G2=MAX($B2:$G2)))*1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -445,8 +445,8 @@
         <v>409</v>
       </c>
       <c r="H4" s="2" t="n">
-        <f aca="true">SUMPRODUCT(--(B4:G4=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B4:G4)-COLUMN(B$2),7,1))))/7</f>
-        <v>3</v>
+        <f aca="false">SUMPRODUCT(($B2:$G2=MAX($B2:$G2)))*1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -472,8 +472,8 @@
         <v>227</v>
       </c>
       <c r="H5" s="2" t="n">
-        <f aca="true">SUMPRODUCT(--(B5:G5=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B5:G5)-COLUMN(B$2),7,1))))/7</f>
-        <v>0</v>
+        <f aca="false">SUMPRODUCT(($B2:$G2=MAX($B2:$G2)))*1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -499,8 +499,8 @@
         <v>212</v>
       </c>
       <c r="H6" s="2" t="n">
-        <f aca="true">SUMPRODUCT(--(B6:G6=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B6:G6)-COLUMN(B$2),7,1))))/7</f>
-        <v>0</v>
+        <f aca="false">SUMPRODUCT(($B2:$G2=MAX($B2:$G2)))*1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -526,7 +526,7 @@
         <v>343</v>
       </c>
       <c r="H7" s="2" t="n">
-        <f aca="true">SUMPRODUCT(--(B7:G7=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B7:G7)-COLUMN(B$2),7,1))))/7</f>
+        <f aca="false">SUMPRODUCT(($B2:$G2=MAX($B2:$G2)))*1</f>
         <v>1</v>
       </c>
     </row>
@@ -553,8 +553,8 @@
         <v>199</v>
       </c>
       <c r="H8" s="2" t="n">
-        <f aca="true">SUMPRODUCT(--(B8:G8=SUBTOTAL(4,OFFSET(B$2,0,COLUMN(B8:G8)-COLUMN(B$2),7,1))))/7</f>
-        <v>0</v>
+        <f aca="false">SUMPRODUCT(($B2:$G2=MAX($B2:$G2)))*1</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
